--- a/spreadsheet_template.xlsx
+++ b/spreadsheet_template.xlsx
@@ -620,18 +620,15 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="8.359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="6.3515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="10" style="1" width="5.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="1" width="12.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="10" style="1" width="3.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8614,18 +8611,18 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="8.359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="6.3515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="4.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="7.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="10" style="1" width="5.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="3.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="5.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="5.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="4.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="5.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="6.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="10" style="1" width="3.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
